--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0002_ses-01_pet_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0002_ses-01_pet_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -967,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="V3" s="0">
-        <v>0.030637254901960786</v>
+        <v>0.030637254901960787</v>
       </c>
       <c r="W3" s="0">
         <v>0</v>
       </c>
       <c r="X3" s="0">
-        <v>0.037900322152738294</v>
+        <v>0.037900322152738295</v>
       </c>
       <c r="Y3" s="0">
         <v>0</v>
@@ -1015,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="AL3" s="0">
-        <v>0.058038305281485784</v>
+        <v>0.058038305281485785</v>
       </c>
       <c r="AM3" s="0">
         <v>0.030892801977139329</v>
@@ -1739,7 +1740,7 @@
         <v>0.029715474333259047</v>
       </c>
       <c r="AL5" s="0">
-        <v>0.0967305088024763</v>
+        <v>0.096730508802476301</v>
       </c>
       <c r="AM5" s="0">
         <v>0</v>
@@ -1808,7 +1809,7 @@
         <v>0.0055778670236501559</v>
       </c>
       <c r="BI5" s="0">
-        <v>0.046620046620046623</v>
+        <v>0.046620046620046624</v>
       </c>
       <c r="BJ5" s="0">
         <v>0.03685277317118113</v>
@@ -1898,7 +1899,7 @@
         <v>0.069470759125931536</v>
       </c>
       <c r="CM5" s="0">
-        <v>0.018632383081796162</v>
+        <v>0.018632383081796163</v>
       </c>
       <c r="CN5" s="0">
         <v>0.023929169657812877</v>
@@ -2200,7 +2201,7 @@
         <v>0.024218939210462583</v>
       </c>
       <c r="BS6" s="0">
-        <v>0.0080778706732905214</v>
+        <v>0.0080778706732905215</v>
       </c>
       <c r="BT6" s="0">
         <v>0</v>
@@ -2260,7 +2261,7 @@
         <v>0.056839712012125808</v>
       </c>
       <c r="CM6" s="0">
-        <v>0.018632383081796162</v>
+        <v>0.018632383081796163</v>
       </c>
       <c r="CN6" s="0">
         <v>0.011964584828906439</v>
@@ -2463,7 +2464,7 @@
         <v>0.014857737166629524</v>
       </c>
       <c r="AL7" s="0">
-        <v>0.16766621525762559</v>
+        <v>0.1676662152576256</v>
       </c>
       <c r="AM7" s="0">
         <v>0</v>
@@ -2619,10 +2620,10 @@
         <v>0.002838087129274869</v>
       </c>
       <c r="CL7" s="0">
-        <v>0.097890615131994443</v>
+        <v>0.097890615131994444</v>
       </c>
       <c r="CM7" s="0">
-        <v>0.018632383081796162</v>
+        <v>0.018632383081796163</v>
       </c>
       <c r="CN7" s="0">
         <v>0.047858339315625754</v>
@@ -2783,7 +2784,7 @@
         <v>0.017094017094017096</v>
       </c>
       <c r="X8" s="0">
-        <v>0.037900322152738294</v>
+        <v>0.037900322152738295</v>
       </c>
       <c r="Y8" s="0">
         <v>0.026205450733752623</v>
@@ -2882,7 +2883,7 @@
         <v>0.013703323055841042</v>
       </c>
       <c r="BE8" s="0">
-        <v>0.062509767151117362</v>
+        <v>0.062509767151117363</v>
       </c>
       <c r="BF8" s="0">
         <v>0</v>
@@ -2981,7 +2982,7 @@
         <v>0.005676174258549738</v>
       </c>
       <c r="CL8" s="0">
-        <v>0.097890615131994443</v>
+        <v>0.097890615131994444</v>
       </c>
       <c r="CM8" s="0">
         <v>0</v>
@@ -3217,7 +3218,7 @@
         <v>0.0061819980217606282</v>
       </c>
       <c r="AV9" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW9" s="0">
         <v>0.017940437746681002</v>
@@ -3241,7 +3242,7 @@
         <v>0.12273573726087682</v>
       </c>
       <c r="BD9" s="0">
-        <v>0.020554984583761544</v>
+        <v>0.020554984583761545</v>
       </c>
       <c r="BE9" s="0">
         <v>0.078137208938896641</v>
@@ -3259,7 +3260,7 @@
         <v>0.078895463510848057</v>
       </c>
       <c r="BJ9" s="0">
-        <v>0.081076100976598411</v>
+        <v>0.081076100976598412</v>
       </c>
       <c r="BK9" s="0">
         <v>0.013737207225770988</v>
@@ -3289,7 +3290,7 @@
         <v>0.04846722403974308</v>
       </c>
       <c r="BT9" s="0">
-        <v>0.016959213092512491</v>
+        <v>0.016959213092512492</v>
       </c>
       <c r="BU9" s="0">
         <v>0.11397782613200695</v>
@@ -3313,7 +3314,7 @@
         <v>0.10025062656641595</v>
       </c>
       <c r="CB9" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC9" s="0">
         <v>0.087489063867016548</v>
@@ -3355,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="CP9" s="0">
-        <v>0.075948355118519328</v>
+        <v>0.075948355118519329</v>
       </c>
       <c r="CQ9" s="0">
         <v>0</v>
@@ -3510,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="Y10" s="0">
-        <v>0.078616352201257927</v>
+        <v>0.078616352201257928</v>
       </c>
       <c r="Z10" s="0">
         <v>0</v>
@@ -3603,7 +3604,7 @@
         <v>0.13120027086507546</v>
       </c>
       <c r="BD10" s="0">
-        <v>0.034258307639602636</v>
+        <v>0.034258307639602637</v>
       </c>
       <c r="BE10" s="0">
         <v>0.062509767151117432</v>
@@ -3624,7 +3625,7 @@
         <v>0.10687304219642539</v>
       </c>
       <c r="BK10" s="0">
-        <v>0.020605810838656521</v>
+        <v>0.020605810838656522</v>
       </c>
       <c r="BL10" s="0">
         <v>0.082792001018978545</v>
@@ -3642,7 +3643,7 @@
         <v>0.036743092298647889</v>
       </c>
       <c r="BQ10" s="0">
-        <v>0.083752093802345134</v>
+        <v>0.083752093802345135</v>
       </c>
       <c r="BR10" s="0">
         <v>0.056510858157746077</v>
@@ -3696,7 +3697,7 @@
         <v>0.044167660439026583</v>
       </c>
       <c r="CI10" s="0">
-        <v>0.088740987243483171</v>
+        <v>0.088740987243483172</v>
       </c>
       <c r="CJ10" s="0">
         <v>0.42167404596247138</v>
@@ -3863,7 +3864,7 @@
         <v>0.055772448410485176</v>
       </c>
       <c r="V11" s="0">
-        <v>0.29105392156862719</v>
+        <v>0.2910539215686272</v>
       </c>
       <c r="W11" s="0">
         <v>0.017094017094017078</v>
@@ -3917,7 +3918,7 @@
         <v>0.092678405931417893</v>
       </c>
       <c r="AN11" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO11" s="0">
         <v>0.059925093632958754</v>
@@ -3965,7 +3966,7 @@
         <v>0.16929067208396803</v>
       </c>
       <c r="BD11" s="0">
-        <v>0.054813292223364118</v>
+        <v>0.054813292223364119</v>
       </c>
       <c r="BE11" s="0">
         <v>0.078137208938896641</v>
@@ -3980,7 +3981,7 @@
         <v>0.011155734047300301</v>
       </c>
       <c r="BI11" s="0">
-        <v>0.15779092702169611</v>
+        <v>0.15779092702169612</v>
       </c>
       <c r="BJ11" s="0">
         <v>0.14372581536760629</v>
@@ -4013,7 +4014,7 @@
         <v>0.072700836059614624</v>
       </c>
       <c r="BT11" s="0">
-        <v>0.0084796065462562457</v>
+        <v>0.0084796065462562458</v>
       </c>
       <c r="BU11" s="0">
         <v>0.11397782613200695</v>
@@ -4052,7 +4053,7 @@
         <v>0.11514104778353472</v>
       </c>
       <c r="CG11" s="0">
-        <v>0.35454706612302755</v>
+        <v>0.35454706612302756</v>
       </c>
       <c r="CH11" s="0">
         <v>0.048584426482929155</v>
@@ -4234,7 +4235,7 @@
         <v>0.018950161076369168</v>
       </c>
       <c r="Y12" s="0">
-        <v>0.078616352201257927</v>
+        <v>0.078616352201257928</v>
       </c>
       <c r="Z12" s="0">
         <v>0</v>
@@ -4330,7 +4331,7 @@
         <v>0.054813292223364223</v>
       </c>
       <c r="BE12" s="0">
-        <v>0.04688232536333807</v>
+        <v>0.046882325363338071</v>
       </c>
       <c r="BF12" s="0">
         <v>0.013883104262113023</v>
@@ -4429,7 +4430,7 @@
         <v>0.034057045551298459</v>
       </c>
       <c r="CL12" s="0">
-        <v>0.23998989516230917</v>
+        <v>0.23998989516230918</v>
       </c>
       <c r="CM12" s="0">
         <v>0.074529532327184719</v>
@@ -4441,7 +4442,7 @@
         <v>0.04408004936965533</v>
       </c>
       <c r="CP12" s="0">
-        <v>0.14789942838869582</v>
+        <v>0.14789942838869583</v>
       </c>
       <c r="CQ12" s="0">
         <v>0</v>
@@ -4590,7 +4591,7 @@
         <v>0.35232843137254871</v>
       </c>
       <c r="W13" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X13" s="0">
         <v>0.11370096645821479</v>
@@ -4641,16 +4642,16 @@
         <v>0.18535681186283579</v>
       </c>
       <c r="AN13" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO13" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP13" s="0">
         <v>0.1618837380426783</v>
       </c>
       <c r="AQ13" s="0">
-        <v>0.2288984263233188</v>
+        <v>0.22889842632331881</v>
       </c>
       <c r="AR13" s="0">
         <v>0.062305295950155708</v>
@@ -4716,7 +4717,7 @@
         <v>0.12100369379696843</v>
       </c>
       <c r="BM13" s="0">
-        <v>0.092705255229155722</v>
+        <v>0.092705255229155723</v>
       </c>
       <c r="BN13" s="0">
         <v>0.15523129462899707</v>
@@ -4964,7 +4965,7 @@
         <v>0.045756119881034132</v>
       </c>
       <c r="AA14" s="0">
-        <v>0.20521841102316057</v>
+        <v>0.20521841102316058</v>
       </c>
       <c r="AB14" s="0">
         <v>0.061312078479460512</v>
@@ -4985,7 +4986,7 @@
         <v>0.060359136864342897</v>
       </c>
       <c r="AH14" s="0">
-        <v>0.52331113225499581</v>
+        <v>0.52331113225499582</v>
       </c>
       <c r="AI14" s="0">
         <v>0.65876152832674639</v>
@@ -5090,7 +5091,7 @@
         <v>0.066137566137566203</v>
       </c>
       <c r="BQ14" s="0">
-        <v>0.083752093802345134</v>
+        <v>0.083752093802345135</v>
       </c>
       <c r="BR14" s="0">
         <v>0.15338661499959652</v>
@@ -5135,13 +5136,13 @@
         <v>0.38095238095238132</v>
       </c>
       <c r="CF14" s="0">
-        <v>0.51813471502590724</v>
+        <v>0.51813471502590725</v>
       </c>
       <c r="CG14" s="0">
         <v>0.56136618802812788</v>
       </c>
       <c r="CH14" s="0">
-        <v>0.09716885296585849</v>
+        <v>0.097168852965858491</v>
       </c>
       <c r="CI14" s="0">
         <v>0.077648363838047768</v>
@@ -5365,7 +5366,7 @@
         <v>0.18535681186283579</v>
       </c>
       <c r="AN15" s="0">
-        <v>0.17383746197305502</v>
+        <v>0.17383746197305503</v>
       </c>
       <c r="AO15" s="0">
         <v>0.044943820224719058</v>
@@ -5488,7 +5489,7 @@
         <v>0.4199475065616794</v>
       </c>
       <c r="CC15" s="0">
-        <v>0.074990626171728469</v>
+        <v>0.07499062617172847</v>
       </c>
       <c r="CD15" s="0">
         <v>0.14102564102564089</v>
@@ -5500,7 +5501,7 @@
         <v>0.57570523891767367</v>
       </c>
       <c r="CG15" s="0">
-        <v>0.69136677893990361</v>
+        <v>0.69136677893990362</v>
       </c>
       <c r="CH15" s="0">
         <v>0.13691974736098217</v>
@@ -5709,7 +5710,7 @@
         <v>0.030179568432171448</v>
       </c>
       <c r="AH16" s="0">
-        <v>0.68981921979067617</v>
+        <v>0.68981921979067618</v>
       </c>
       <c r="AI16" s="0">
         <v>0.65876152832674639</v>
@@ -5811,7 +5812,7 @@
         <v>0.078802206461781002</v>
       </c>
       <c r="BP16" s="0">
-        <v>0.080834803057025353</v>
+        <v>0.080834803057025354</v>
       </c>
       <c r="BQ16" s="0">
         <v>0.14357501794687738</v>
@@ -5832,7 +5833,7 @@
         <v>0.40950040950040989</v>
       </c>
       <c r="BW16" s="0">
-        <v>0.46783625730994199</v>
+        <v>0.467836257309942</v>
       </c>
       <c r="BX16" s="0">
         <v>0.29448885149347948</v>
@@ -5862,7 +5863,7 @@
         <v>1.2089810017271168</v>
       </c>
       <c r="CG16" s="0">
-        <v>0.76818530993322764</v>
+        <v>0.76818530993322765</v>
       </c>
       <c r="CH16" s="0">
         <v>0.17225387571220369</v>
@@ -5889,7 +5890,7 @@
         <v>0.061712069117517469</v>
       </c>
       <c r="CP16" s="0">
-        <v>0.30379342047407792</v>
+        <v>0.30379342047407793</v>
       </c>
       <c r="CQ16" s="0">
         <v>0</v>
@@ -6092,7 +6093,7 @@
         <v>0.43459365493263763</v>
       </c>
       <c r="AO17" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP17" s="0">
         <v>0.44150110375275897</v>
@@ -6164,7 +6165,7 @@
         <v>0.27385046490892856</v>
       </c>
       <c r="BM17" s="0">
-        <v>0.15644011819920028</v>
+        <v>0.15644011819920029</v>
       </c>
       <c r="BN17" s="0">
         <v>0.30011383628272764</v>
@@ -6203,7 +6204,7 @@
         <v>0.33444816053511678</v>
       </c>
       <c r="BZ17" s="0">
-        <v>0.40810953133227978</v>
+        <v>0.40810953133227979</v>
       </c>
       <c r="CA17" s="0">
         <v>0.050125313283207976</v>
@@ -6418,7 +6419,7 @@
         <v>0.1839362354383812</v>
       </c>
       <c r="AC18" s="0">
-        <v>0.59101654846335649</v>
+        <v>0.5910165484633565</v>
       </c>
       <c r="AD18" s="0">
         <v>0</v>
@@ -6436,7 +6437,7 @@
         <v>0.80875356803044651</v>
       </c>
       <c r="AI18" s="0">
-        <v>0.83105300496604761</v>
+        <v>0.83105300496604762</v>
       </c>
       <c r="AJ18" s="0">
         <v>0.34055727554179532</v>
@@ -6445,7 +6446,7 @@
         <v>0.27486813758264594</v>
       </c>
       <c r="AL18" s="0">
-        <v>0.98665118978525745</v>
+        <v>0.98665118978525746</v>
       </c>
       <c r="AM18" s="0">
         <v>0.40160642570281091</v>
@@ -6541,7 +6542,7 @@
         <v>0.21536252692031568</v>
       </c>
       <c r="BR18" s="0">
-        <v>0.28255429078872984</v>
+        <v>0.28255429078872985</v>
       </c>
       <c r="BS18" s="0">
         <v>0.31907589159497524</v>
@@ -6574,7 +6575,7 @@
         <v>0.2099737532808397</v>
       </c>
       <c r="CC18" s="0">
-        <v>0.24996875390576156</v>
+        <v>0.24996875390576157</v>
       </c>
       <c r="CD18" s="0">
         <v>0.23076923076923056</v>
@@ -6592,7 +6593,7 @@
         <v>0.26942272867806172</v>
       </c>
       <c r="CI18" s="0">
-        <v>0.26622296173044901</v>
+        <v>0.26622296173044902</v>
       </c>
       <c r="CJ18" s="0">
         <v>0.99093400801180598</v>
@@ -6610,7 +6611,7 @@
         <v>0.38286671452500565</v>
       </c>
       <c r="CO18" s="0">
-        <v>0.13224014810896575</v>
+        <v>0.13224014810896576</v>
       </c>
       <c r="CP18" s="0">
         <v>0.40772274853099855</v>
@@ -6813,7 +6814,7 @@
         <v>0.64874884151992773</v>
       </c>
       <c r="AN19" s="0">
-        <v>0.56497175141243094</v>
+        <v>0.56497175141243095</v>
       </c>
       <c r="AO19" s="0">
         <v>0.1048689138576782</v>
@@ -6867,7 +6868,7 @@
         <v>0.34380371933114645</v>
       </c>
       <c r="BF19" s="0">
-        <v>0.041649312786339147</v>
+        <v>0.041649312786339148</v>
       </c>
       <c r="BG19" s="0">
         <v>0.29574861367837418</v>
@@ -6897,7 +6898,7 @@
         <v>0.14634695485759355</v>
       </c>
       <c r="BP19" s="0">
-        <v>0.14697236919459183</v>
+        <v>0.14697236919459184</v>
       </c>
       <c r="BQ19" s="0">
         <v>0.31107920555156826</v>
@@ -6954,7 +6955,7 @@
         <v>0.22967183428293866</v>
       </c>
       <c r="CI19" s="0">
-        <v>0.32168607875762711</v>
+        <v>0.32168607875762712</v>
       </c>
       <c r="CJ19" s="0">
         <v>1.2017710309930458</v>
@@ -7124,10 +7125,10 @@
         <v>0.85784313725490113</v>
       </c>
       <c r="W20" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X20" s="0">
-        <v>0.36005306045101348</v>
+        <v>0.36005306045101349</v>
       </c>
       <c r="Y20" s="0">
         <v>0.70754716981132004</v>
@@ -7178,7 +7179,7 @@
         <v>0.78226857887874768</v>
       </c>
       <c r="AO20" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP20" s="0">
         <v>0.60338484179543728</v>
@@ -7193,7 +7194,7 @@
         <v>0.79365079365079294</v>
       </c>
       <c r="AT20" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU20" s="0">
         <v>0.12982195845697317</v>
@@ -7217,7 +7218,7 @@
         <v>0.50330292544825372</v>
       </c>
       <c r="BB20" s="0">
-        <v>0.43366844076483307</v>
+        <v>0.43366844076483308</v>
       </c>
       <c r="BC20" s="0">
         <v>0.74487895716945929</v>
@@ -7262,7 +7263,7 @@
         <v>0.19841269841269824</v>
       </c>
       <c r="BQ20" s="0">
-        <v>0.35893754486719281</v>
+        <v>0.35893754486719282</v>
       </c>
       <c r="BR20" s="0">
         <v>0.46823282473560951</v>
@@ -7280,7 +7281,7 @@
         <v>0.68796068796068732</v>
       </c>
       <c r="BW20" s="0">
-        <v>0.73099415204678297</v>
+        <v>0.73099415204678298</v>
       </c>
       <c r="BX20" s="0">
         <v>0.29448885149347892</v>
@@ -7307,7 +7308,7 @@
         <v>0.7619047619047612</v>
       </c>
       <c r="CF20" s="0">
-        <v>0.80598733448474313</v>
+        <v>0.80598733448474314</v>
       </c>
       <c r="CG20" s="0">
         <v>1.0222773739880626</v>
@@ -7420,7 +7421,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.040252787505534723</v>
+        <v>0.040252787505534724</v>
       </c>
       <c r="B21" s="0">
         <v>0.0041813012209399522</v>
@@ -7492,7 +7493,7 @@
         <v>0.53060451013833576</v>
       </c>
       <c r="Y21" s="0">
-        <v>0.68134171907756746</v>
+        <v>0.68134171907756747</v>
       </c>
       <c r="Z21" s="0">
         <v>0.22878059940517023</v>
@@ -7600,7 +7601,7 @@
         <v>0.29562695225345798</v>
       </c>
       <c r="BI21" s="0">
-        <v>0.79254079254079179</v>
+        <v>0.7925407925407918</v>
       </c>
       <c r="BJ21" s="0">
         <v>0.70388796756955896</v>
@@ -7642,7 +7643,7 @@
         <v>0.62244062244062193</v>
       </c>
       <c r="BW21" s="0">
-        <v>0.80409356725146119</v>
+        <v>0.8040935672514612</v>
       </c>
       <c r="BX21" s="0">
         <v>0.57495442434441113</v>
@@ -7654,13 +7655,13 @@
         <v>0.85571353343865109</v>
       </c>
       <c r="CA21" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB21" s="0">
         <v>0.36745406824146948</v>
       </c>
       <c r="CC21" s="0">
-        <v>0.32495938007749003</v>
+        <v>0.32495938007749004</v>
       </c>
       <c r="CD21" s="0">
         <v>0.51282051282051244</v>
@@ -7687,7 +7688,7 @@
         <v>0.23839931885908877</v>
       </c>
       <c r="CL21" s="0">
-        <v>0.92838196286472074</v>
+        <v>0.92838196286472075</v>
       </c>
       <c r="CM21" s="0">
         <v>0.54033910937208818</v>
@@ -7878,7 +7879,7 @@
         <v>0.070175438596491169</v>
       </c>
       <c r="AG22" s="0">
-        <v>0.26407122378149966</v>
+        <v>0.26407122378149967</v>
       </c>
       <c r="AH22" s="0">
         <v>1.1100539169045345</v>
@@ -7905,7 +7906,7 @@
         <v>0.35955056179775247</v>
       </c>
       <c r="AP22" s="0">
-        <v>0.88300220750551794</v>
+        <v>0.88300220750551795</v>
       </c>
       <c r="AQ22" s="0">
         <v>0.44349070100143023</v>
@@ -7986,13 +7987,13 @@
         <v>0.23515579071134604</v>
       </c>
       <c r="BQ22" s="0">
-        <v>0.35893754486719281</v>
+        <v>0.35893754486719282</v>
       </c>
       <c r="BR22" s="0">
         <v>0.46823282473560951</v>
       </c>
       <c r="BS22" s="0">
-        <v>0.58968455915020745</v>
+        <v>0.58968455915020746</v>
       </c>
       <c r="BT22" s="0">
         <v>0.16535232765199681</v>
@@ -8183,7 +8184,7 @@
         <v>0.027720027720027799</v>
       </c>
       <c r="N23" s="0">
-        <v>0.072689511941848597</v>
+        <v>0.072689511941848598</v>
       </c>
       <c r="O23" s="0">
         <v>0.013183046602069776</v>
@@ -8285,7 +8286,7 @@
         <v>0.25964391691394734</v>
       </c>
       <c r="AV23" s="0">
-        <v>0.52164840897235409</v>
+        <v>0.5216484089723541</v>
       </c>
       <c r="AW23" s="0">
         <v>0.49336203803372941</v>
@@ -8399,7 +8400,7 @@
         <v>1.2054600248182981</v>
       </c>
       <c r="CH23" s="0">
-        <v>0.61834724614637337</v>
+        <v>0.61834724614637338</v>
       </c>
       <c r="CI23" s="0">
         <v>0.76539101497504369</v>
@@ -8533,7 +8534,7 @@
         <v>0.038759689922480585</v>
       </c>
       <c r="J24" s="0">
-        <v>0.044759895133959927</v>
+        <v>0.044759895133959928</v>
       </c>
       <c r="K24" s="0">
         <v>0.038008361839604682</v>
@@ -8542,7 +8543,7 @@
         <v>0.035517670040845287</v>
       </c>
       <c r="M24" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N24" s="0">
         <v>0.07268951194184832</v>
@@ -8650,7 +8651,7 @@
         <v>0.56636112974141095</v>
       </c>
       <c r="AW24" s="0">
-        <v>0.52027269465374903</v>
+        <v>0.52027269465374904</v>
       </c>
       <c r="AX24" s="0">
         <v>0.6887470880178258</v>
@@ -8731,7 +8732,7 @@
         <v>0.9649122807017535</v>
       </c>
       <c r="BX24" s="0">
-        <v>0.77128032534006385</v>
+        <v>0.77128032534006386</v>
       </c>
       <c r="BY24" s="0">
         <v>0.97547380156075725</v>
@@ -8907,7 +8908,7 @@
         <v>0.013860013860013849</v>
       </c>
       <c r="N25" s="0">
-        <v>0.041536863966770476</v>
+        <v>0.041536863966770477</v>
       </c>
       <c r="O25" s="0">
         <v>0.013183046602069728</v>
@@ -8937,7 +8938,7 @@
         <v>0.4957264957264953</v>
       </c>
       <c r="X25" s="0">
-        <v>0.73905628197839623</v>
+        <v>0.73905628197839624</v>
       </c>
       <c r="Y25" s="0">
         <v>1.1006289308176092</v>
@@ -9461,7 +9462,7 @@
         <v>1.1705685618729085</v>
       </c>
       <c r="BZ26" s="0">
-        <v>1.0926803580832007</v>
+        <v>1.0926803580832008</v>
       </c>
       <c r="CA26" s="0">
         <v>0.60150375939849576</v>
@@ -9808,7 +9809,7 @@
         <v>0.51725599932163102</v>
       </c>
       <c r="BU27" s="0">
-        <v>1.2744793285669866</v>
+        <v>1.2744793285669867</v>
       </c>
       <c r="BV27" s="0">
         <v>0.98280098280098194</v>
@@ -9957,7 +9958,7 @@
         <v>0.16101115002213948</v>
       </c>
       <c r="B28" s="0">
-        <v>0.087807325639739336</v>
+        <v>0.087807325639739337</v>
       </c>
       <c r="C28" s="0">
         <v>0.10899985270290206</v>
@@ -10032,7 +10033,7 @@
         <v>0.52619537863189358</v>
       </c>
       <c r="AA28" s="0">
-        <v>1.2899442978598687</v>
+        <v>1.2899442978598688</v>
       </c>
       <c r="AB28" s="0">
         <v>0.63355814428775981</v>
@@ -10233,7 +10234,7 @@
         <v>0.67442475535572788</v>
       </c>
       <c r="CP28" s="0">
-        <v>1.1752008634128825</v>
+        <v>1.1752008634128826</v>
       </c>
       <c r="CQ28" s="0">
         <v>2.1673168617251903</v>
@@ -10263,7 +10264,7 @@
         <v>0.0081043844719993745</v>
       </c>
       <c r="CZ28" s="0">
-        <v>2.3615318884486975</v>
+        <v>2.3615318884486976</v>
       </c>
       <c r="DA28" s="0">
         <v>0.21613832853025997</v>
@@ -10284,10 +10285,10 @@
         <v>0.54533060668030153</v>
       </c>
       <c r="DG28" s="0">
-        <v>0.50813008130081438</v>
+        <v>0.50813008130081439</v>
       </c>
       <c r="DH28" s="0">
-        <v>1.8716577540107004</v>
+        <v>1.8716577540107005</v>
       </c>
       <c r="DI28" s="0">
         <v>0</v>
@@ -10454,7 +10455,7 @@
         <v>1.3355592654424029</v>
       </c>
       <c r="AU29" s="0">
-        <v>0.6985657764589509</v>
+        <v>0.69856577645895091</v>
       </c>
       <c r="AV29" s="0">
         <v>0.9762277367911163</v>
@@ -10496,13 +10497,13 @@
         <v>1.0263275323516279</v>
       </c>
       <c r="BI29" s="0">
-        <v>1.380670611439841</v>
+        <v>1.3806706114398411</v>
       </c>
       <c r="BJ29" s="0">
         <v>1.2972176156255746</v>
       </c>
       <c r="BK29" s="0">
-        <v>0.7761522082560609</v>
+        <v>0.77615220825606091</v>
       </c>
       <c r="BL29" s="0">
         <v>1.1336135524137043</v>
@@ -10637,7 +10638,7 @@
         <v>0.74090704984283717</v>
       </c>
       <c r="DD29" s="0">
-        <v>2.762598664238006</v>
+        <v>2.7625986642380061</v>
       </c>
       <c r="DE29" s="0">
         <v>0.66054454647978034</v>
@@ -10720,7 +10721,7 @@
         <v>0.22845275181723759</v>
       </c>
       <c r="O30" s="0">
-        <v>0.098872849515522956</v>
+        <v>0.098872849515522957</v>
       </c>
       <c r="P30" s="0">
         <v>0.15924472501848361</v>
@@ -10765,7 +10766,7 @@
         <v>1.4184397163120555</v>
       </c>
       <c r="AD30" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE30" s="0">
         <v>0.40983606557377011</v>
@@ -10888,7 +10889,7 @@
         <v>1.2513118592072323</v>
       </c>
       <c r="BS30" s="0">
-        <v>1.1712912476271244</v>
+        <v>1.1712912476271245</v>
       </c>
       <c r="BT30" s="0">
         <v>0.68260832697362783</v>
@@ -10921,7 +10922,7 @@
         <v>1.3623297087864004</v>
       </c>
       <c r="CD30" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="CE30" s="0">
         <v>1.0158730158730149</v>
@@ -10948,7 +10949,7 @@
         <v>1.4715169887583668</v>
       </c>
       <c r="CM30" s="0">
-        <v>0.96888392025339964</v>
+        <v>0.96888392025339965</v>
       </c>
       <c r="CN30" s="0">
         <v>1.3161043311797069</v>
@@ -10978,7 +10979,7 @@
         <v>0.12437810945273621</v>
       </c>
       <c r="CW30" s="0">
-        <v>3.2641669700279063</v>
+        <v>3.2641669700279064</v>
       </c>
       <c r="CX30" s="0">
         <v>4.2345797379354391</v>
@@ -11073,7 +11074,7 @@
         <v>0.28506271379703513</v>
       </c>
       <c r="L31" s="0">
-        <v>0.23086485526549438</v>
+        <v>0.23086485526549439</v>
       </c>
       <c r="M31" s="0">
         <v>0.11088011088011079</v>
@@ -11127,7 +11128,7 @@
         <v>1.4657210401891241</v>
       </c>
       <c r="AD31" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE31" s="0">
         <v>0.75136612021857863</v>
@@ -11235,7 +11236,7 @@
         <v>1.1414334550089797</v>
       </c>
       <c r="BN31" s="0">
-        <v>1.366035392735174</v>
+        <v>1.3660353927351741</v>
       </c>
       <c r="BO31" s="0">
         <v>1.1370032646628381</v>
@@ -11283,10 +11284,10 @@
         <v>1.2998375203099601</v>
       </c>
       <c r="CD31" s="0">
-        <v>1.3974358974358962</v>
+        <v>1.3974358974358963</v>
       </c>
       <c r="CE31" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="CF31" s="0">
         <v>0.97869890616004518</v>
@@ -11301,13 +11302,13 @@
         <v>1.1092623405435376</v>
       </c>
       <c r="CJ31" s="0">
-        <v>1.3598987982289676</v>
+        <v>1.3598987982289677</v>
       </c>
       <c r="CK31" s="0">
         <v>0.91670214275578177</v>
       </c>
       <c r="CL31" s="0">
-        <v>1.3104711380573439</v>
+        <v>1.310471138057344</v>
       </c>
       <c r="CM31" s="0">
         <v>1.3228991988075263</v>
@@ -11417,7 +11418,7 @@
         <v>0.22116313117154221</v>
       </c>
       <c r="F32" s="0">
-        <v>0.35006169119967961</v>
+        <v>0.35006169119967962</v>
       </c>
       <c r="G32" s="0">
         <v>0.093482905982906248</v>
@@ -11624,10 +11625,10 @@
         <v>1.4086814086814126</v>
       </c>
       <c r="BW32" s="0">
-        <v>1.4766081871345071</v>
+        <v>1.4766081871345072</v>
       </c>
       <c r="BX32" s="0">
-        <v>1.2620950778291999</v>
+        <v>1.2620950778292</v>
       </c>
       <c r="BY32" s="0">
         <v>1.2681159420289891</v>
@@ -11717,7 +11718,7 @@
         <v>2.2334293948126862</v>
       </c>
       <c r="DB32" s="0">
-        <v>4.6760710553814135</v>
+        <v>4.6760710553814136</v>
       </c>
       <c r="DC32" s="0">
         <v>2.7166591827570801</v>
@@ -11881,7 +11882,7 @@
         <v>1.5446400988569648</v>
       </c>
       <c r="AN33" s="0">
-        <v>1.260321599304649</v>
+        <v>1.2603215993046491</v>
       </c>
       <c r="AO33" s="0">
         <v>0.94382022471910032</v>
@@ -11890,7 +11891,7 @@
         <v>1.280353200883001</v>
       </c>
       <c r="AQ33" s="0">
-        <v>1.373390557939913</v>
+        <v>1.3733905579399131</v>
       </c>
       <c r="AR33" s="0">
         <v>1.221183800623052</v>
@@ -12013,10 +12014,10 @@
         <v>1.3968253968253954</v>
       </c>
       <c r="CF33" s="0">
-        <v>0.80598733448474313</v>
+        <v>0.80598733448474314</v>
       </c>
       <c r="CG33" s="0">
-        <v>1.1109141405188196</v>
+        <v>1.1109141405188197</v>
       </c>
       <c r="CH33" s="0">
         <v>1.2366944922927423</v>
@@ -12064,7 +12065,7 @@
         <v>0.062189054726368105</v>
       </c>
       <c r="CW33" s="0">
-        <v>1.4561339643247166</v>
+        <v>1.4561339643247167</v>
       </c>
       <c r="CX33" s="0">
         <v>1.9335250878875023</v>
@@ -12079,7 +12080,7 @@
         <v>2.6657060518731965</v>
       </c>
       <c r="DB33" s="0">
-        <v>4.2580982236154616</v>
+        <v>4.2580982236154617</v>
       </c>
       <c r="DC33" s="0">
         <v>3.2779524023349769</v>
@@ -12222,7 +12223,7 @@
         <v>0.91228070175438514</v>
       </c>
       <c r="AG34" s="0">
-        <v>1.1241889240983844</v>
+        <v>1.1241889240983845</v>
       </c>
       <c r="AH34" s="0">
         <v>1.1179828734538524</v>
@@ -12342,10 +12343,10 @@
         <v>1.0599508182820307</v>
       </c>
       <c r="BU34" s="0">
-        <v>1.2744793285669866</v>
+        <v>1.2744793285669867</v>
       </c>
       <c r="BV34" s="0">
-        <v>1.3759213759213746</v>
+        <v>1.3759213759213747</v>
       </c>
       <c r="BW34" s="0">
         <v>1.3742690058479521</v>
@@ -12551,7 +12552,7 @@
         <v>1.2827663134411589</v>
       </c>
       <c r="V35" s="0">
-        <v>1.3020833333333321</v>
+        <v>1.3020833333333322</v>
       </c>
       <c r="W35" s="0">
         <v>1.264957264957264</v>
@@ -12701,13 +12702,13 @@
         <v>1.3086150490730633</v>
       </c>
       <c r="BT35" s="0">
-        <v>1.1320274739252087</v>
+        <v>1.1320274739252088</v>
       </c>
       <c r="BU35" s="0">
         <v>1.3573722930266281</v>
       </c>
       <c r="BV35" s="0">
-        <v>1.0483210483210474</v>
+        <v>1.0483210483210475</v>
       </c>
       <c r="BW35" s="0">
         <v>1.154970760233917</v>
@@ -12725,10 +12726,10 @@
         <v>1.0526315789473675</v>
       </c>
       <c r="CB35" s="0">
-        <v>1.8372703412073474</v>
+        <v>1.8372703412073475</v>
       </c>
       <c r="CC35" s="0">
-        <v>1.2123484564429436</v>
+        <v>1.2123484564429437</v>
       </c>
       <c r="CD35" s="0">
         <v>1.3717948717948705</v>
@@ -12743,7 +12744,7 @@
         <v>1.0104591384506285</v>
       </c>
       <c r="CH35" s="0">
-        <v>1.3647807075659188</v>
+        <v>1.3647807075659189</v>
       </c>
       <c r="CI35" s="0">
         <v>1.4642262895174696</v>
@@ -12764,7 +12765,7 @@
         <v>1.4716439339554903</v>
       </c>
       <c r="CO35" s="0">
-        <v>1.115225249052278</v>
+        <v>1.1152252490522781</v>
       </c>
       <c r="CP35" s="0">
         <v>1.2751329096214563</v>
@@ -12850,7 +12851,7 @@
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>0.70844906009741115</v>
+        <v>0.70844906009741116</v>
       </c>
       <c r="B36" s="0">
         <v>0.39304231476835561</v>
@@ -12955,7 +12956,7 @@
         <v>0.80064862673558246</v>
       </c>
       <c r="AJ36" s="0">
-        <v>1.176470588235293</v>
+        <v>1.1764705882352931</v>
       </c>
       <c r="AK36" s="0">
         <v>1.3223386078300263</v>
@@ -13009,13 +13010,13 @@
         <v>1.0904896718045498</v>
       </c>
       <c r="BB36" s="0">
-        <v>1.3897102306327604</v>
+        <v>1.3897102306327605</v>
       </c>
       <c r="BC36" s="0">
         <v>1.1892669713898754</v>
       </c>
       <c r="BD36" s="0">
-        <v>1.2949640287769772</v>
+        <v>1.2949640287769773</v>
       </c>
       <c r="BE36" s="0">
         <v>1.1564306922956702</v>
@@ -13045,7 +13046,7 @@
         <v>1.3268439654672912</v>
       </c>
       <c r="BN36" s="0">
-        <v>1.5212666873641711</v>
+        <v>1.5212666873641712</v>
       </c>
       <c r="BO36" s="0">
         <v>1.2720927614544624</v>
@@ -13215,7 +13216,7 @@
         <v>0.65209515758966252</v>
       </c>
       <c r="B37" s="0">
-        <v>0.57701956848971347</v>
+        <v>0.57701956848971348</v>
       </c>
       <c r="C37" s="0">
         <v>0.56856679923405462</v>
@@ -13329,7 +13330,7 @@
         <v>1.4210688909484079</v>
       </c>
       <c r="AN37" s="0">
-        <v>1.260321599304649</v>
+        <v>1.2603215993046491</v>
       </c>
       <c r="AO37" s="0">
         <v>1.1835205992509352</v>
@@ -13365,7 +13366,7 @@
         <v>0.95045500505561087</v>
       </c>
       <c r="AZ37" s="0">
-        <v>1.2659009509694938</v>
+        <v>1.2659009509694939</v>
       </c>
       <c r="BA37" s="0">
         <v>1.3316556569151714</v>
@@ -13518,7 +13519,7 @@
         <v>0.095877277085330698</v>
       </c>
       <c r="CY37" s="0">
-        <v>1.4587892049598818</v>
+        <v>1.4587892049598819</v>
       </c>
       <c r="CZ37" s="0">
         <v>0.87003806416530649</v>
@@ -13566,7 +13567,7 @@
         <v>3.1901041666666639</v>
       </c>
       <c r="DO37" s="0">
-        <v>2.9126213592232983</v>
+        <v>2.9126213592232984</v>
       </c>
       <c r="DP37" s="0">
         <v>0.70422535211267545</v>
@@ -13631,7 +13632,7 @@
         <v>0.45509426952726217</v>
       </c>
       <c r="T38" s="0">
-        <v>0.66926176329987463</v>
+        <v>0.66926176329987464</v>
       </c>
       <c r="U38" s="0">
         <v>1.4686744748094538</v>
@@ -13670,7 +13671,7 @@
         <v>1.4736842105263253</v>
       </c>
       <c r="AG38" s="0">
-        <v>1.3580805794477226</v>
+        <v>1.3580805794477227</v>
       </c>
       <c r="AH38" s="0">
         <v>0.67396130669204379</v>
@@ -13679,7 +13680,7 @@
         <v>0.67903111381372694</v>
       </c>
       <c r="AJ38" s="0">
-        <v>1.1042311661506778</v>
+        <v>1.1042311661506779</v>
       </c>
       <c r="AK38" s="0">
         <v>1.3371963449966657</v>
@@ -13712,7 +13713,7 @@
         <v>1.8920422927100848</v>
       </c>
       <c r="AU38" s="0">
-        <v>1.267309594460938</v>
+        <v>1.2673095944609381</v>
       </c>
       <c r="AV38" s="0">
         <v>1.1774349802518893</v>
@@ -13751,7 +13752,7 @@
         <v>1.3370301910043216</v>
       </c>
       <c r="BH38" s="0">
-        <v>1.2884872824631945</v>
+        <v>1.2884872824631946</v>
       </c>
       <c r="BI38" s="0">
         <v>1.0507441276672114</v>
@@ -13808,7 +13809,7 @@
         <v>1.2374934175882122</v>
       </c>
       <c r="CA38" s="0">
-        <v>1.1528822055137919</v>
+        <v>1.152882205513792</v>
       </c>
       <c r="CB38" s="0">
         <v>1.1023622047244166</v>
@@ -13889,7 +13890,7 @@
         <v>3.3141210374639982</v>
       </c>
       <c r="DB38" s="0">
-        <v>1.0710553814002159</v>
+        <v>1.071055381400216</v>
       </c>
       <c r="DC38" s="0">
         <v>2.5520131716809025</v>
@@ -13925,7 +13926,7 @@
         <v>3.5612535612535843</v>
       </c>
       <c r="DN38" s="0">
-        <v>2.0182291666666798</v>
+        <v>2.0182291666666799</v>
       </c>
       <c r="DO38" s="0">
         <v>1.9417475728155467</v>
@@ -13942,7 +13943,7 @@
         <v>0.6355577855828729</v>
       </c>
       <c r="C39" s="0">
-        <v>0.63926940639269358</v>
+        <v>0.63926940639269359</v>
       </c>
       <c r="D39" s="0">
         <v>0.6529519438297402</v>
@@ -14065,7 +14066,7 @@
         <v>1.173104434907009</v>
       </c>
       <c r="AR39" s="0">
-        <v>1.1713395638629271</v>
+        <v>1.1713395638629272</v>
       </c>
       <c r="AS39" s="0">
         <v>0.92592592592592504</v>
@@ -14092,7 +14093,7 @@
         <v>1.272076077559589</v>
       </c>
       <c r="BA39" s="0">
-        <v>0.97514941805599153</v>
+        <v>0.97514941805599154</v>
       </c>
       <c r="BB39" s="0">
         <v>1.094027202838556</v>
@@ -14110,7 +14111,7 @@
         <v>1.4577259475218645</v>
       </c>
       <c r="BG39" s="0">
-        <v>1.3062230437461479</v>
+        <v>1.306223043746148</v>
       </c>
       <c r="BH39" s="0">
         <v>1.2940651494868349</v>
@@ -14179,16 +14180,16 @@
         <v>1.2373453318335197</v>
       </c>
       <c r="CD39" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="CE39" s="0">
-        <v>0.82539682539682468</v>
+        <v>0.82539682539682469</v>
       </c>
       <c r="CF39" s="0">
         <v>0.6908462867012084</v>
       </c>
       <c r="CG39" s="0">
-        <v>0.69136677893990361</v>
+        <v>0.69136677893990362</v>
       </c>
       <c r="CH39" s="0">
         <v>1.3426968773464059</v>
@@ -14206,7 +14207,7 @@
         <v>0.88417329796640065</v>
       </c>
       <c r="CM39" s="0">
-        <v>1.3787963480529148</v>
+        <v>1.3787963480529149</v>
       </c>
       <c r="CN39" s="0">
         <v>1.2203876525484554</v>
@@ -14221,13 +14222,13 @@
         <v>0.39011703511053286</v>
       </c>
       <c r="CR39" s="0">
-        <v>0.34089698519228689</v>
+        <v>0.3408969851922869</v>
       </c>
       <c r="CS39" s="0">
         <v>1.850213769718412</v>
       </c>
       <c r="CT39" s="0">
-        <v>3.1504472033106365</v>
+        <v>3.1504472033106366</v>
       </c>
       <c r="CU39" s="0">
         <v>4.5908183632734492</v>
@@ -14361,7 +14362,7 @@
         <v>1.0039040713887331</v>
       </c>
       <c r="V40" s="0">
-        <v>0.61274509803921517</v>
+        <v>0.61274509803921518</v>
       </c>
       <c r="W40" s="0">
         <v>1.4529914529914516</v>
@@ -14460,7 +14461,7 @@
         <v>1.1827321111768174</v>
       </c>
       <c r="BC40" s="0">
-        <v>0.86338242762823691</v>
+        <v>0.86338242762823692</v>
       </c>
       <c r="BD40" s="0">
         <v>1.1373758136348056</v>
@@ -14675,7 +14676,7 @@
         <v>0.81612310375977248</v>
       </c>
       <c r="F41" s="0">
-        <v>1.0042753436056346</v>
+        <v>1.0042753436056347</v>
       </c>
       <c r="G41" s="0">
         <v>0.81463675213675146</v>
@@ -14696,7 +14697,7 @@
         <v>0.81690641093944172</v>
       </c>
       <c r="M41" s="0">
-        <v>0.65142065142065086</v>
+        <v>0.65142065142065087</v>
       </c>
       <c r="N41" s="0">
         <v>0.88265835929387249</v>
@@ -14720,7 +14721,7 @@
         <v>0.99706344328347929</v>
       </c>
       <c r="U41" s="0">
-        <v>1.3571295779884724</v>
+        <v>1.3571295779884725</v>
       </c>
       <c r="V41" s="0">
         <v>0.5514705882352936</v>
@@ -14747,7 +14748,7 @@
         <v>0.54373522458628787</v>
       </c>
       <c r="AD41" s="0">
-        <v>0.54722817035450821</v>
+        <v>0.54722817035450822</v>
       </c>
       <c r="AE41" s="0">
         <v>1.5027322404371573</v>
@@ -14771,7 +14772,7 @@
         <v>1.1143302874972132</v>
       </c>
       <c r="AL41" s="0">
-        <v>0.54169084929386679</v>
+        <v>0.5416908492938668</v>
       </c>
       <c r="AM41" s="0">
         <v>1.0812480691998754</v>
@@ -14819,13 +14820,13 @@
         <v>1.1324315822585709</v>
       </c>
       <c r="BB41" s="0">
-        <v>1.1038833037650297</v>
+        <v>1.1038833037650298</v>
       </c>
       <c r="BC41" s="0">
         <v>0.72794988996106247</v>
       </c>
       <c r="BD41" s="0">
-        <v>1.2949640287769772</v>
+        <v>1.2949640287769773</v>
       </c>
       <c r="BE41" s="0">
         <v>0.98452883263009761</v>
@@ -14837,7 +14838,7 @@
         <v>1.090573012939001</v>
       </c>
       <c r="BH41" s="0">
-        <v>1.2717536813922345</v>
+        <v>1.2717536813922346</v>
       </c>
       <c r="BI41" s="0">
         <v>0.87860857091626254</v>
@@ -14861,7 +14862,7 @@
         <v>1.4184397163120555</v>
       </c>
       <c r="BP41" s="0">
-        <v>1.2492651381540258</v>
+        <v>1.2492651381540259</v>
       </c>
       <c r="BQ41" s="0">
         <v>1.3041397463508004</v>
@@ -14906,7 +14907,7 @@
         <v>1.3205128205128194</v>
       </c>
       <c r="CE41" s="0">
-        <v>0.82539682539682468</v>
+        <v>0.82539682539682469</v>
       </c>
       <c r="CF41" s="0">
         <v>0.63327576280944098</v>
@@ -14927,7 +14928,7 @@
         <v>1.2686249467858652</v>
       </c>
       <c r="CL41" s="0">
-        <v>0.72628520904382909</v>
+        <v>0.7262852090438291</v>
       </c>
       <c r="CM41" s="0">
         <v>1.3974287311347109</v>
@@ -15008,13 +15009,13 @@
         <v>0.6527415143603128</v>
       </c>
       <c r="DM41" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="DN41" s="0">
         <v>0.26041666666666646</v>
       </c>
       <c r="DO41" s="0">
-        <v>0.40453074433656921</v>
+        <v>0.40453074433656922</v>
       </c>
       <c r="DP41" s="0">
         <v>0</v>
@@ -15049,7 +15050,7 @@
         <v>0.88039867109634473</v>
       </c>
       <c r="J42" s="0">
-        <v>1.1126031076155753</v>
+        <v>1.1126031076155754</v>
       </c>
       <c r="K42" s="0">
         <v>0.8741923223109076</v>
@@ -15124,7 +15125,7 @@
         <v>0.58674278464953955</v>
       </c>
       <c r="AI42" s="0">
-        <v>0.43579608797000063</v>
+        <v>0.43579608797000064</v>
       </c>
       <c r="AJ42" s="0">
         <v>0.90815273477812097</v>
@@ -15175,7 +15176,7 @@
         <v>1.2942366026289169</v>
       </c>
       <c r="AZ42" s="0">
-        <v>1.2659009509694938</v>
+        <v>1.2659009509694939</v>
       </c>
       <c r="BA42" s="0">
         <v>0.8493236866939281</v>
@@ -15220,7 +15221,7 @@
         <v>0.91069026182344948</v>
       </c>
       <c r="BO42" s="0">
-        <v>1.2946076775863999</v>
+        <v>1.2946076775864</v>
       </c>
       <c r="BP42" s="0">
         <v>1.4182833627278058</v>
@@ -15310,7 +15311,7 @@
         <v>0.026632576968147414</v>
       </c>
       <c r="CS42" s="0">
-        <v>0.56022408963585379</v>
+        <v>0.5602240896358538</v>
       </c>
       <c r="CT42" s="0">
         <v>0.95447870778267174</v>
@@ -15477,7 +15478,7 @@
         <v>1.9125683060109273</v>
       </c>
       <c r="AF43" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="AG43" s="0">
         <v>1.2901765504753269</v>
@@ -15627,7 +15628,7 @@
         <v>0.92488438945131768</v>
       </c>
       <c r="CD43" s="0">
-        <v>0.8846153846153838</v>
+        <v>0.88461538461538381</v>
       </c>
       <c r="CE43" s="0">
         <v>0.69841269841269771</v>
@@ -15839,10 +15840,10 @@
         <v>1.092896174863387</v>
       </c>
       <c r="AF44" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="AG44" s="0">
-        <v>1.1468236004225127</v>
+        <v>1.1468236004225128</v>
       </c>
       <c r="AH44" s="0">
         <v>0.25372660957817927</v>
@@ -15914,7 +15915,7 @@
         <v>1.1236724905789646</v>
       </c>
       <c r="BE44" s="0">
-        <v>0.90639162369120096</v>
+        <v>0.90639162369120097</v>
       </c>
       <c r="BF44" s="0">
         <v>1.0828821324448137</v>
@@ -15929,7 +15930,7 @@
         <v>0.61681907835753935</v>
       </c>
       <c r="BJ44" s="0">
-        <v>0.59332964805601573</v>
+        <v>0.59332964805601574</v>
       </c>
       <c r="BK44" s="0">
         <v>1.2500858575451601</v>
@@ -15947,7 +15948,7 @@
         <v>1.0131712259371826</v>
       </c>
       <c r="BP44" s="0">
-        <v>1.1537330981775415</v>
+        <v>1.1537330981775416</v>
       </c>
       <c r="BQ44" s="0">
         <v>1.0528834649437655</v>
@@ -16034,7 +16035,7 @@
         <v>0</v>
       </c>
       <c r="CS44" s="0">
-        <v>0.1326846528084917</v>
+        <v>0.13268465280849171</v>
       </c>
       <c r="CT44" s="0">
         <v>0.34708316646642612</v>
@@ -16171,7 +16172,7 @@
         <v>0.61349693251533688</v>
       </c>
       <c r="V45" s="0">
-        <v>0.29105392156862719</v>
+        <v>0.2910539215686272</v>
       </c>
       <c r="W45" s="0">
         <v>1.2136752136752125</v>
@@ -16180,7 +16181,7 @@
         <v>0.92855789274208755</v>
       </c>
       <c r="Y45" s="0">
-        <v>0.44549266247379415</v>
+        <v>0.44549266247379416</v>
       </c>
       <c r="Z45" s="0">
         <v>1.1896591169068853</v>
@@ -16396,7 +16397,7 @@
         <v>0</v>
       </c>
       <c r="CS45" s="0">
-        <v>0.04422821760283057</v>
+        <v>0.044228217602830571</v>
       </c>
       <c r="CT45" s="0">
         <v>0.12014417300760902</v>
@@ -16405,7 +16406,7 @@
         <v>1.2974051896207575</v>
       </c>
       <c r="CV45" s="0">
-        <v>2.1144278606965154</v>
+        <v>2.1144278606965155</v>
       </c>
       <c r="CW45" s="0">
         <v>0</v>
@@ -16554,7 +16555,7 @@
         <v>0.85836909871245193</v>
       </c>
       <c r="AC46" s="0">
-        <v>0.44917257683215422</v>
+        <v>0.44917257683215423</v>
       </c>
       <c r="AD46" s="0">
         <v>0.99928622412563106</v>
@@ -16590,7 +16591,7 @@
         <v>0.52151238591916904</v>
       </c>
       <c r="AO46" s="0">
-        <v>1.0636704119850255</v>
+        <v>1.0636704119850256</v>
       </c>
       <c r="AP46" s="0">
         <v>0.50036791758646393</v>
@@ -16722,7 +16723,7 @@
         <v>0.17271157167530338</v>
       </c>
       <c r="CG46" s="0">
-        <v>0.24818294628612111</v>
+        <v>0.24818294628612112</v>
       </c>
       <c r="CH46" s="0">
         <v>0.79501788790248296</v>
@@ -16788,7 +16789,7 @@
         <v>0</v>
       </c>
       <c r="DC46" s="0">
-        <v>0.0074839095943721482</v>
+        <v>0.0074839095943721483</v>
       </c>
       <c r="DD46" s="0">
         <v>0</v>
@@ -16868,7 +16869,7 @@
         <v>1.2786361214704305</v>
       </c>
       <c r="M47" s="0">
-        <v>1.2612612612612601</v>
+        <v>1.2612612612612602</v>
       </c>
       <c r="N47" s="0">
         <v>1.5160955347871221</v>
@@ -16877,7 +16878,7 @@
         <v>1.1073759145738571</v>
       </c>
       <c r="P47" s="0">
-        <v>1.2398339305010508</v>
+        <v>1.2398339305010509</v>
       </c>
       <c r="Q47" s="0">
         <v>1.4403292181069944</v>
@@ -16889,7 +16890,7 @@
         <v>1.3049131605832625</v>
       </c>
       <c r="T47" s="0">
-        <v>1.3453527282660644</v>
+        <v>1.3453527282660645</v>
       </c>
       <c r="U47" s="0">
         <v>0.70645101319947878</v>
@@ -16901,7 +16902,7 @@
         <v>0.90598290598290521</v>
       </c>
       <c r="X47" s="0">
-        <v>0.79590676520750347</v>
+        <v>0.79590676520750348</v>
       </c>
       <c r="Y47" s="0">
         <v>0.57651991614255715</v>
@@ -16934,7 +16935,7 @@
         <v>0.19029495718363446</v>
       </c>
       <c r="AI47" s="0">
-        <v>0.21283064761325612</v>
+        <v>0.21283064761325613</v>
       </c>
       <c r="AJ47" s="0">
         <v>0.51599587203302333</v>
@@ -17015,7 +17016,7 @@
         <v>0.3048233817464584</v>
       </c>
       <c r="BJ47" s="0">
-        <v>0.45697438732264561</v>
+        <v>0.45697438732264562</v>
       </c>
       <c r="BK47" s="0">
         <v>0.85857545161068682</v>
@@ -17033,7 +17034,7 @@
         <v>0.92311156140943285</v>
       </c>
       <c r="BP47" s="0">
-        <v>0.94062316284538416</v>
+        <v>0.94062316284538417</v>
       </c>
       <c r="BQ47" s="0">
         <v>0.71787508973438563</v>
@@ -17042,7 +17043,7 @@
         <v>0.57318156131428055</v>
       </c>
       <c r="BS47" s="0">
-        <v>0.61391817117007907</v>
+        <v>0.61391817117007908</v>
       </c>
       <c r="BT47" s="0">
         <v>1.1744255066564899</v>
@@ -17359,7 +17360,7 @@
         <v>0.27509734213644804</v>
       </c>
       <c r="BD48" s="0">
-        <v>0.71257279890373348</v>
+        <v>0.71257279890373349</v>
       </c>
       <c r="BE48" s="0">
         <v>0.50007813720893846</v>
@@ -17449,7 +17450,7 @@
         <v>0.1181823553743425</v>
       </c>
       <c r="CH48" s="0">
-        <v>0.62276401219027377</v>
+        <v>0.62276401219027378</v>
       </c>
       <c r="CI48" s="0">
         <v>0.75429839156960554</v>
@@ -17467,7 +17468,7 @@
         <v>0.68939817402645742</v>
       </c>
       <c r="CN48" s="0">
-        <v>0.40679588418281853</v>
+        <v>0.40679588418281854</v>
       </c>
       <c r="CO48" s="0">
         <v>0.95653707132151899</v>
@@ -17595,7 +17596,7 @@
         <v>1.3444213444213433</v>
       </c>
       <c r="N49" s="0">
-        <v>1.3084112149532698</v>
+        <v>1.3084112149532699</v>
       </c>
       <c r="O49" s="0">
         <v>1.2194318106914497</v>
@@ -17649,7 +17650,7 @@
         <v>0.88797814207650194</v>
       </c>
       <c r="AF49" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="AG49" s="0">
         <v>0.72430964237211348</v>
@@ -17817,7 +17818,7 @@
         <v>0.52135330005546265</v>
       </c>
       <c r="CJ49" s="0">
-        <v>0.084334809192494128</v>
+        <v>0.084334809192494129</v>
       </c>
       <c r="CK49" s="0">
         <v>0.82304526748971119</v>
@@ -17829,7 +17830,7 @@
         <v>0.65213340786286511</v>
       </c>
       <c r="CN49" s="0">
-        <v>0.35893754486719281</v>
+        <v>0.35893754486719282</v>
       </c>
       <c r="CO49" s="0">
         <v>0.84192894296041543</v>
@@ -17957,7 +17958,7 @@
         <v>1.2474012474012464</v>
       </c>
       <c r="N50" s="0">
-        <v>1.4537902388369663</v>
+        <v>1.4537902388369664</v>
       </c>
       <c r="O50" s="0">
         <v>1.3248961835080075</v>
@@ -17966,7 +17967,7 @@
         <v>1.5298868224990034</v>
       </c>
       <c r="Q50" s="0">
-        <v>1.5946502057613154</v>
+        <v>1.5946502057613155</v>
       </c>
       <c r="R50" s="0">
         <v>1.4233241505968766</v>
@@ -18014,7 +18015,7 @@
         <v>0.63157894736842057</v>
       </c>
       <c r="AG50" s="0">
-        <v>0.7771238871284134</v>
+        <v>0.77712388712841341</v>
       </c>
       <c r="AH50" s="0">
         <v>0.10307643514113533</v>
@@ -18032,7 +18033,7 @@
         <v>0.10317920938930795</v>
       </c>
       <c r="AM50" s="0">
-        <v>0.52517763361136804</v>
+        <v>0.52517763361136805</v>
       </c>
       <c r="AN50" s="0">
         <v>0.26075619295958258</v>
@@ -18280,7 +18281,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>1.380670611439841</v>
+        <v>1.3806706114398411</v>
       </c>
       <c r="B51" s="0">
         <v>1.3129285833751452</v>
@@ -18657,7 +18658,7 @@
         <v>1.3238638133507759</v>
       </c>
       <c r="F52" s="0">
-        <v>1.2768643654414495</v>
+        <v>1.2768643654414496</v>
       </c>
       <c r="G52" s="0">
         <v>1.3087606837606827</v>
@@ -18759,7 +18760,7 @@
         <v>0.46339202965708948</v>
       </c>
       <c r="AN52" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO52" s="0">
         <v>0.55430711610486849</v>
@@ -18786,7 +18787,7 @@
         <v>0.52910052910052863</v>
       </c>
       <c r="AW52" s="0">
-        <v>0.39468963042698207</v>
+        <v>0.39468963042698208</v>
       </c>
       <c r="AX52" s="0">
         <v>0.30385900941962901</v>
@@ -18822,7 +18823,7 @@
         <v>0.46854082998661267</v>
       </c>
       <c r="BI52" s="0">
-        <v>0.16854939931862994</v>
+        <v>0.16854939931862995</v>
       </c>
       <c r="BJ52" s="0">
         <v>0.27271052146674013</v>
@@ -19214,7 +19215,7 @@
         <v>0.33099216920965502</v>
       </c>
       <c r="BS53" s="0">
-        <v>0.17367421947574604</v>
+        <v>0.17367421947574605</v>
       </c>
       <c r="BT53" s="0">
         <v>0.74196557279742159</v>
@@ -19238,10 +19239,10 @@
         <v>0.11848341232227477</v>
       </c>
       <c r="CA53" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB53" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC53" s="0">
         <v>0.33745781777277811</v>
@@ -19390,7 +19391,7 @@
         <v>1.4027651629831455</v>
       </c>
       <c r="I54" s="0">
-        <v>1.22923588039867</v>
+        <v>1.2292358803986701</v>
       </c>
       <c r="J54" s="0">
         <v>0.99750623441396413</v>
@@ -19525,7 +19526,7 @@
         <v>0.13631120897556873</v>
       </c>
       <c r="BB54" s="0">
-        <v>0.23654642223536348</v>
+        <v>0.23654642223536349</v>
       </c>
       <c r="BC54" s="0">
         <v>0.088877602844083206</v>
@@ -19588,7 +19589,7 @@
         <v>0.11466011466011455</v>
       </c>
       <c r="BW54" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX54" s="0">
         <v>0.098162950497826307</v>
@@ -19603,7 +19604,7 @@
         <v>0.2005012531328319</v>
       </c>
       <c r="CB54" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC54" s="0">
         <v>0.27496562929633772</v>
@@ -19764,7 +19765,7 @@
         <v>1.5982951518380497</v>
       </c>
       <c r="M55" s="0">
-        <v>1.1503811503811578</v>
+        <v>1.1503811503811579</v>
       </c>
       <c r="N55" s="0">
         <v>1.2772585669782015</v>
@@ -19902,16 +19903,16 @@
         <v>0.74968763015410733</v>
       </c>
       <c r="BG55" s="0">
-        <v>0.22797288971041429</v>
+        <v>0.2279728897104143</v>
       </c>
       <c r="BH55" s="0">
         <v>0.3514056224899621</v>
       </c>
       <c r="BI55" s="0">
-        <v>0.071723148646226031</v>
+        <v>0.071723148646226032</v>
       </c>
       <c r="BJ55" s="0">
-        <v>0.12529942878201666</v>
+        <v>0.12529942878201667</v>
       </c>
       <c r="BK55" s="0">
         <v>0.4395906312246749</v>
@@ -20093,7 +20094,7 @@
         <v>0.95399106388117294</v>
       </c>
       <c r="B56" s="0">
-        <v>1.2669342699448058</v>
+        <v>1.2669342699448059</v>
       </c>
       <c r="C56" s="0">
         <v>1.08410664309913</v>
@@ -20300,7 +20301,7 @@
         <v>0.15338661499959622</v>
       </c>
       <c r="BS56" s="0">
-        <v>0.17367421947574604</v>
+        <v>0.17367421947574605</v>
       </c>
       <c r="BT56" s="0">
         <v>0.4070211142202998</v>
@@ -20518,7 +20519,7 @@
         <v>0.030637254901960755</v>
       </c>
       <c r="W57" s="0">
-        <v>0.20512820512820495</v>
+        <v>0.20512820512820496</v>
       </c>
       <c r="X57" s="0">
         <v>0.15160128861095304</v>
@@ -20662,7 +20663,7 @@
         <v>0.056510858157745973</v>
       </c>
       <c r="BS57" s="0">
-        <v>0.1292459307726482</v>
+        <v>0.12924593077264821</v>
       </c>
       <c r="BT57" s="0">
         <v>0.39854150767404362</v>
@@ -20674,7 +20675,7 @@
         <v>0.098280098280098191</v>
       </c>
       <c r="BW57" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX57" s="0">
         <v>0.08413967185527968</v>
@@ -20686,7 +20687,7 @@
         <v>0.078988941548183186</v>
       </c>
       <c r="CA57" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB57" s="0">
         <v>0.10498687664041985</v>
@@ -20958,7 +20959,7 @@
         <v>0.20865936358894088</v>
       </c>
       <c r="AW58" s="0">
-        <v>0.14352350197344801</v>
+        <v>0.14352350197344802</v>
       </c>
       <c r="AX58" s="0">
         <v>0.15192950470981451</v>
@@ -21054,7 +21055,7 @@
         <v>0.15748031496062978</v>
       </c>
       <c r="CC58" s="0">
-        <v>0.074990626171728469</v>
+        <v>0.07499062617172847</v>
       </c>
       <c r="CD58" s="0">
         <v>0.076923076923076858</v>
@@ -21329,7 +21330,7 @@
         <v>0.43141220087630566</v>
       </c>
       <c r="AZ59" s="0">
-        <v>0.28405582314437416</v>
+        <v>0.28405582314437417</v>
       </c>
       <c r="BA59" s="0">
         <v>0.073398343294536997</v>
@@ -21341,10 +21342,10 @@
         <v>0.021161334010496004</v>
       </c>
       <c r="BD59" s="0">
-        <v>0.054813292223364118</v>
+        <v>0.054813292223364119</v>
       </c>
       <c r="BE59" s="0">
-        <v>0.031254883575558653</v>
+        <v>0.031254883575558654</v>
       </c>
       <c r="BF59" s="0">
         <v>0.56920727474663291</v>
@@ -21356,7 +21357,7 @@
         <v>0.10597947344935288</v>
       </c>
       <c r="BI59" s="0">
-        <v>0.032275416890801475</v>
+        <v>0.032275416890801476</v>
       </c>
       <c r="BJ59" s="0">
         <v>0.047908605122535426</v>
@@ -21413,7 +21414,7 @@
         <v>0.10025062656641595</v>
       </c>
       <c r="CB59" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC59" s="0">
         <v>0.099987501562304626</v>
@@ -21541,7 +21542,7 @@
         <v>0.55548846757637915</v>
       </c>
       <c r="B60" s="0">
-        <v>0.94915537715336928</v>
+        <v>0.94915537715336929</v>
       </c>
       <c r="C60" s="0">
         <v>0.77772867874502805</v>
@@ -21568,7 +21569,7 @@
         <v>0.671398427009399</v>
       </c>
       <c r="K60" s="0">
-        <v>0.91220068415051236</v>
+        <v>0.91220068415051237</v>
       </c>
       <c r="L60" s="0">
         <v>0.74587107085775106</v>
@@ -21625,7 +21626,7 @@
         <v>0.047281323877068522</v>
       </c>
       <c r="AD60" s="0">
-        <v>1.0706638115631681</v>
+        <v>1.0706638115631682</v>
       </c>
       <c r="AE60" s="0">
         <v>0.27322404371584674</v>
@@ -21769,13 +21770,13 @@
         <v>0</v>
       </c>
       <c r="BZ60" s="0">
-        <v>0.026329647182727726</v>
+        <v>0.026329647182727727</v>
       </c>
       <c r="CA60" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB60" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC60" s="0">
         <v>0.062492188476440391</v>
@@ -21909,7 +21910,7 @@
         <v>0.77772867874502805</v>
       </c>
       <c r="D61" s="0">
-        <v>0.95074174248012377</v>
+        <v>0.95074174248012378</v>
       </c>
       <c r="E61" s="0">
         <v>0.7600535775472691</v>
@@ -21936,7 +21937,7 @@
         <v>0.78138874089859645</v>
       </c>
       <c r="M61" s="0">
-        <v>0.91476091476091403</v>
+        <v>0.91476091476091404</v>
       </c>
       <c r="N61" s="0">
         <v>0.53997923156801619</v>
@@ -21966,7 +21967,7 @@
         <v>0</v>
       </c>
       <c r="W61" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X61" s="0">
         <v>0.13265112753458394</v>
@@ -22020,7 +22021,7 @@
         <v>0</v>
       </c>
       <c r="AO61" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP61" s="0">
         <v>0.0441501103752759</v>
@@ -22155,7 +22156,7 @@
         <v>0</v>
       </c>
       <c r="CH61" s="0">
-        <v>0.075085022746345056</v>
+        <v>0.075085022746345057</v>
       </c>
       <c r="CI61" s="0">
         <v>0.022185246810870751</v>
@@ -22271,7 +22272,7 @@
         <v>0.64810723228752332</v>
       </c>
       <c r="D62" s="0">
-        <v>0.83599704942217778</v>
+        <v>0.83599704942217779</v>
       </c>
       <c r="E62" s="0">
         <v>0.6323396567299</v>
@@ -22427,7 +22428,7 @@
         <v>0.0084645336041984012</v>
       </c>
       <c r="BD62" s="0">
-        <v>0.054813292223364118</v>
+        <v>0.054813292223364119</v>
       </c>
       <c r="BE62" s="0">
         <v>0</v>
@@ -22499,10 +22500,10 @@
         <v>0.050125313283207976</v>
       </c>
       <c r="CB62" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC62" s="0">
-        <v>0.074990626171728469</v>
+        <v>0.07499062617172847</v>
       </c>
       <c r="CD62" s="0">
         <v>0.038461538461538429</v>
@@ -22995,7 +22996,7 @@
         <v>0.52143172779496205</v>
       </c>
       <c r="D64" s="0">
-        <v>0.59831161380214692</v>
+        <v>0.59831161380214693</v>
       </c>
       <c r="E64" s="0">
         <v>0.6011899199451759</v>
@@ -23154,7 +23155,7 @@
         <v>0.041109969167523089</v>
       </c>
       <c r="BE64" s="0">
-        <v>0.031254883575558653</v>
+        <v>0.031254883575558654</v>
       </c>
       <c r="BF64" s="0">
         <v>0.24989587671803393</v>
@@ -23193,7 +23194,7 @@
         <v>0.011964584828906426</v>
       </c>
       <c r="BR64" s="0">
-        <v>0.024218939210462562</v>
+        <v>0.024218939210462563</v>
       </c>
       <c r="BS64" s="0">
         <v>0.020194676683226286</v>
@@ -23217,7 +23218,7 @@
         <v>0.013935340022296532</v>
       </c>
       <c r="BZ64" s="0">
-        <v>0.026329647182727726</v>
+        <v>0.026329647182727727</v>
       </c>
       <c r="CA64" s="0">
         <v>0</v>
@@ -23226,7 +23227,7 @@
         <v>0</v>
       </c>
       <c r="CC64" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD64" s="0">
         <v>0</v>
@@ -23588,7 +23589,7 @@
         <v>0</v>
       </c>
       <c r="CC65" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD65" s="0">
         <v>0.064102564102564055</v>
@@ -23606,7 +23607,7 @@
         <v>0</v>
       </c>
       <c r="CI65" s="0">
-        <v>0.044370493621741502</v>
+        <v>0.044370493621741503</v>
       </c>
       <c r="CJ65" s="0">
         <v>0</v>
@@ -23713,7 +23714,7 @@
         <v>0.26164311878597568</v>
       </c>
       <c r="B66" s="0">
-        <v>0.48503094162903448</v>
+        <v>0.48503094162903449</v>
       </c>
       <c r="C66" s="0">
         <v>0.3328914420385915</v>
@@ -23749,10 +23750,10 @@
         <v>0.52668052668052623</v>
       </c>
       <c r="N66" s="0">
-        <v>0.32191069574247116</v>
+        <v>0.32191069574247117</v>
       </c>
       <c r="O66" s="0">
-        <v>0.55368795728692854</v>
+        <v>0.55368795728692855</v>
       </c>
       <c r="P66" s="0">
         <v>0.32986407325257322</v>
@@ -23830,7 +23831,7 @@
         <v>0</v>
       </c>
       <c r="AO66" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP66" s="0">
         <v>0.014716703458425299</v>
@@ -23848,7 +23849,7 @@
         <v>0</v>
       </c>
       <c r="AU66" s="0">
-        <v>0.037091988130563767</v>
+        <v>0.037091988130563768</v>
       </c>
       <c r="AV66" s="0">
         <v>0.044712720769058759</v>
@@ -23950,7 +23951,7 @@
         <v>0</v>
       </c>
       <c r="CC66" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD66" s="0">
         <v>0</v>
@@ -24072,7 +24073,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>0.2093144950287821</v>
+        <v>0.20931449502878211</v>
       </c>
       <c r="B67" s="0">
         <v>0.37213580866365853</v>
@@ -24264,7 +24265,7 @@
         <v>0.0063686154629983855</v>
       </c>
       <c r="BM67" s="0">
-        <v>0.017382235355466825</v>
+        <v>0.017382235355466826</v>
       </c>
       <c r="BN67" s="0">
         <v>0.010348752975266547</v>
@@ -24282,7 +24283,7 @@
         <v>0</v>
       </c>
       <c r="BS67" s="0">
-        <v>0.0040389353366452867</v>
+        <v>0.0040389353366452868</v>
       </c>
       <c r="BT67" s="0">
         <v>0.033918426185025233</v>
@@ -24841,7 +24842,7 @@
         <v>0.40867444466416453</v>
       </c>
       <c r="P69" s="0">
-        <v>0.25024171074333323</v>
+        <v>0.25024171074333324</v>
       </c>
       <c r="Q69" s="0">
         <v>0.56584362139918065</v>
@@ -25200,7 +25201,7 @@
         <v>0.1246105919003105</v>
       </c>
       <c r="O70" s="0">
-        <v>0.28343550194449701</v>
+        <v>0.28343550194449702</v>
       </c>
       <c r="P70" s="0">
         <v>0.23886708752772368</v>
@@ -25571,7 +25572,7 @@
         <v>0.051440329218107331</v>
       </c>
       <c r="R71" s="0">
-        <v>0.13774104683195681</v>
+        <v>0.13774104683195682</v>
       </c>
       <c r="S71" s="0">
         <v>0.17182130584192551</v>
@@ -25730,7 +25731,7 @@
         <v>0</v>
       </c>
       <c r="BS71" s="0">
-        <v>0.0040389353366452867</v>
+        <v>0.0040389353366452868</v>
       </c>
       <c r="BT71" s="0">
         <v>0.0084796065462563082</v>
@@ -26247,7 +26248,7 @@
         <v>0.052328623757195526</v>
       </c>
       <c r="B73" s="0">
-        <v>0.13798294029101948</v>
+        <v>0.13798294029101949</v>
       </c>
       <c r="C73" s="0">
         <v>0.12078362056267571</v>
@@ -26624,7 +26625,7 @@
         <v>0.045909729993400095</v>
       </c>
       <c r="G74" s="0">
-        <v>0.13354700854700743</v>
+        <v>0.13354700854700744</v>
       </c>
       <c r="H74" s="0">
         <v>0.1009183570491464</v>
@@ -26660,7 +26661,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="0">
-        <v>0.13002693415064442</v>
+        <v>0.13002693415064443</v>
       </c>
       <c r="T74" s="0">
         <v>0.10243802499487724</v>
@@ -26672,7 +26673,7 @@
         <v>0</v>
       </c>
       <c r="W74" s="0">
-        <v>0.017094017094016953</v>
+        <v>0.017094017094016954</v>
       </c>
       <c r="X74" s="0">
         <v>0</v>
@@ -27007,7 +27008,7 @@
         <v>0.083160083160083706</v>
       </c>
       <c r="N75" s="0">
-        <v>0.083073727933541563</v>
+        <v>0.083073727933541564</v>
       </c>
       <c r="O75" s="0">
         <v>0.13842198932173316</v>
@@ -27348,7 +27349,7 @@
         <v>0.02008550687211284</v>
       </c>
       <c r="G76" s="0">
-        <v>0.1335470085470094</v>
+        <v>0.13354700854700941</v>
       </c>
       <c r="H76" s="0">
         <v>0.080734685639318321</v>
@@ -28437,10 +28438,10 @@
         <v>0.053418803418802972</v>
       </c>
       <c r="H79" s="0">
-        <v>0.020183671409829278</v>
+        <v>0.020183671409829279</v>
       </c>
       <c r="I79" s="0">
-        <v>0.0387596899224803</v>
+        <v>0.038759689922480301</v>
       </c>
       <c r="J79" s="0">
         <v>0.0063942707334228004</v>
@@ -28865,7 +28866,7 @@
         <v>0</v>
       </c>
       <c r="AD80" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE80" s="0">
         <v>0</v>
@@ -29146,7 +29147,7 @@
         <v>0.012543903662819766</v>
       </c>
       <c r="C81" s="0">
-        <v>0.0088378258948297993</v>
+        <v>0.0088378258948297994</v>
       </c>
       <c r="D81" s="0">
         <v>0.010928066005518582</v>
@@ -29206,7 +29207,7 @@
         <v>0</v>
       </c>
       <c r="W81" s="0">
-        <v>0.017094017094016953</v>
+        <v>0.017094017094016954</v>
       </c>
       <c r="X81" s="0">
         <v>0</v>
@@ -29589,7 +29590,7 @@
         <v>0</v>
       </c>
       <c r="AD82" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE82" s="0">
         <v>0</v>
@@ -29897,7 +29898,7 @@
         <v>0.019004180919802199</v>
       </c>
       <c r="L83" s="0">
-        <v>0.017758835020422511</v>
+        <v>0.017758835020422512</v>
       </c>
       <c r="M83" s="0">
         <v>0.013860013860013745</v>
@@ -30675,7 +30676,7 @@
         <v>0</v>
       </c>
       <c r="AD85" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE85" s="0">
         <v>0</v>
@@ -32123,7 +32124,7 @@
         <v>0</v>
       </c>
       <c r="AD89" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE89" s="0">
         <v>0</v>
